--- a/public/templates/LeiPort_Import_Template_v1.1.xlsx
+++ b/public/templates/LeiPort_Import_Template_v1.1.xlsx
@@ -654,7 +654,7 @@
     <x:tableColumn id="7" name="樹形"/>
     <x:tableColumn id="8" name="鉢サイズ"/>
     <x:tableColumn id="15" name="入数" dataDxfId="0"/>
-    <x:tableColumn id="9" name="数量"/>
+    <x:tableColumn id="9" name="数量（ケース数）"/>
     <x:tableColumn id="10" name="価格"/>
     <x:tableColumn id="11" name="産地"/>
     <x:tableColumn id="12" name="生産者"/>
